--- a/outputs/reports/gradient_boosting/evaluation.xlsx
+++ b/outputs/reports/gradient_boosting/evaluation.xlsx
@@ -487,37 +487,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9868929521966057</v>
+        <v>0.9843764342318636</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1576198046786282</v>
+        <v>0.167488697081792</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8931788931788932</v>
+        <v>0.9599528857479388</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2679536679536679</v>
+        <v>0.2852143482064742</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9871453178665872</v>
+        <v>0.9844559983116858</v>
       </c>
       <c r="G2" t="n">
-        <v>284824</v>
+        <v>256564</v>
       </c>
       <c r="H2" t="n">
-        <v>3709</v>
+        <v>4051</v>
       </c>
       <c r="I2" t="n">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="J2" t="n">
-        <v>694</v>
+        <v>815</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9769659117168761</v>
+        <v>0.9921433167948055</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5475184683345096</v>
+        <v>0.7271884650078903</v>
       </c>
     </row>
   </sheetData>
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,32 +562,47 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>상위1%양성포착비율(top_1pct_recall)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>상위5%건수(top_5pct_count)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>상위5%양성비율(top_5pct_positive_rate)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>상위5%리프트(top_5pct_lift)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>상위5%양성포착비율(top_5pct_recall)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>상위10%건수(top_10pct_count)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>상위10%양성비율(top_10pct_positive_rate)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>상위10%리프트(top_10pct_lift)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>상위10%양성포착비율(top_10pct_recall)</t>
         </is>
       </c>
     </row>
@@ -598,34 +613,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.002685700459714493</v>
+        <v>0.003247100939326255</v>
       </c>
       <c r="C2" t="n">
-        <v>2894</v>
+        <v>2615</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2335867311679337</v>
+        <v>0.3024856596558317</v>
       </c>
       <c r="E2" t="n">
-        <v>86.97423062315944</v>
+        <v>93.15560720406641</v>
       </c>
       <c r="F2" t="n">
-        <v>14466</v>
+        <v>0.9316843345111896</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05011751693626434</v>
+        <v>13074</v>
       </c>
       <c r="H2" t="n">
-        <v>18.66087364843068</v>
+        <v>0.06348477895058896</v>
       </c>
       <c r="I2" t="n">
-        <v>28931</v>
+        <v>19.55121819026713</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0254398396184024</v>
+        <v>0.9776207302709069</v>
       </c>
       <c r="K2" t="n">
-        <v>9.472329472329472</v>
+        <v>26147</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.03197307530500631</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9.846652722671577</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.9846878680800942</v>
       </c>
     </row>
   </sheetData>
@@ -676,13 +700,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>206993</v>
+        <v>189854</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001207770311073321</v>
+        <v>4.21376426095842e-05</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -695,13 +719,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43642</v>
+        <v>36229</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0003437056046927272</v>
+        <v>0.0001104087885395678</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -714,13 +738,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20296</v>
+        <v>17335</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0003941663381947182</v>
+        <v>0.0002307470435535045</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -733,13 +757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9490</v>
+        <v>8723</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00136986301369863</v>
+        <v>0.001031755130115786</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -752,13 +776,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4470</v>
+        <v>4444</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004921700223713647</v>
+        <v>0.002025202520252025</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -771,13 +795,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2152</v>
+        <v>2293</v>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01672862453531598</v>
+        <v>0.01090274749236808</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -790,13 +814,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>932</v>
+        <v>1127</v>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0407725321888412</v>
+        <v>0.02484472049689441</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -809,13 +833,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>370</v>
+        <v>484</v>
       </c>
       <c r="C9" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.127027027027027</v>
+        <v>0.1198347107438017</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -828,13 +852,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="C10" t="n">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="D10" t="n">
-        <v>0.460093896713615</v>
+        <v>0.4822134387351779</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -847,13 +871,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>752</v>
+        <v>722</v>
       </c>
       <c r="C11" t="n">
-        <v>475</v>
+        <v>582</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6316489361702128</v>
+        <v>0.8060941828254847</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
